--- a/Информация про проект/testplan.xlsx
+++ b/Информация про проект/testplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\vending_machine\Информация про проект\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6634A9-8109-4371-A6B6-4CAD7E66FCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F437864-92B8-45F8-A5AE-2022A9ECF85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
   <si>
     <t>Директория</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>tb/user_srs/user_tests/</t>
-  </si>
-  <si>
-    <t>test_one_coin</t>
   </si>
   <si>
     <t>Проверка корректной работы пользовательского интерфейса при внесении одной монеты (рубли).</t>
@@ -77,9 +74,6 @@
     <t>Успешно пройден</t>
   </si>
   <si>
-    <t>test_few_coin</t>
-  </si>
-  <si>
     <t>Проверка корректной работы пользовательского интерфейса при внесении нескольких монет (рубли).</t>
   </si>
   <si>
@@ -90,32 +84,10 @@
 5) Проверка выданного товара и сдачи</t>
   </si>
   <si>
-    <t>test_change</t>
-  </si>
-  <si>
-    <t>Проверка выдачи сдачи и начисления бонусов (рубли).</t>
-  </si>
-  <si>
-    <t>1) Сброс устройства.
-2) Вход в систему.
-3) Внесение монет: coin_in = 25; currency_type = 0
-4) Выбор товара, подтверждение.
-5) Проверка выданного товара, сдачи и начисления бонусов</t>
-  </si>
-  <si>
-    <t>test_dollars</t>
-  </si>
-  <si>
     <t>Проверка работы с долларами.</t>
   </si>
   <si>
-    <t>test_euros</t>
-  </si>
-  <si>
     <t>Проверка работы с евро.</t>
-  </si>
-  <si>
-    <t>test_random_client_with_no_change</t>
   </si>
   <si>
     <t>Проверка для случайных товаров и разных клиентов (рубли без сдачи).</t>
@@ -126,9 +98,6 @@
 3) Внесение монет, необходимых чтобы сдачи не было.
 4) Выбор товара, подтверждение.
 5) Проверка выданного товара, сдачи и начисления бонусов</t>
-  </si>
-  <si>
-    <t>full_client_session_with_no_errors</t>
   </si>
   <si>
     <t>Проверка полной сессии клиента без ошибок.</t>
@@ -326,9 +295,6 @@
     <t>Тесты обработки ошибок</t>
   </si>
   <si>
-    <t>test_invalid_client_id</t>
-  </si>
-  <si>
     <t>Проверка реакции системы на недопустимый client_id</t>
   </si>
   <si>
@@ -338,9 +304,6 @@
   </si>
   <si>
     <t>Требуется уточнение документации: поведение автомата при недопустимом client_id. На данный момент нет проверки на client_id, автомат просто работает</t>
-  </si>
-  <si>
-    <t>test_invalid_coin_denomination</t>
   </si>
   <si>
     <t>Проверка реакции системы на недопустимые номиналы монет</t>
@@ -352,17 +315,11 @@
 3) Подача монет недоступного номинала</t>
   </si>
   <si>
-    <t>test_insufficient_funds</t>
-  </si>
-  <si>
     <t>Проверка реакции системы на недостаточный баланс при покупке</t>
   </si>
   <si>
     <t>1) Сброс устройства.
 2) Сессия клиента но с условием внесения недостаточных средств</t>
-  </si>
-  <si>
-    <t>test_coin_timeout_refund</t>
   </si>
   <si>
     <t>Проверка возврата средств при таймауте внесения монет</t>
@@ -375,9 +332,6 @@
   </si>
   <si>
     <t>Обнаружен баг: Сдача не возвращается, если истёк таймаут на ожидание</t>
-  </si>
-  <si>
-    <t>test_confirm_timeout_refund</t>
   </si>
   <si>
     <t>Проверка возврата средств при таймауте во время подтверждения покупки</t>
@@ -446,6 +400,39 @@
   </si>
   <si>
     <t>Требуется уточнение спецификации: время появления сигнала access_error</t>
+  </si>
+  <si>
+    <t>one_coin_test</t>
+  </si>
+  <si>
+    <t>few_coin_test</t>
+  </si>
+  <si>
+    <t>dollars_test</t>
+  </si>
+  <si>
+    <t>euros_test</t>
+  </si>
+  <si>
+    <t>random_client_without_change_test</t>
+  </si>
+  <si>
+    <t>client_session_without_errors_test</t>
+  </si>
+  <si>
+    <t>invalid_client_id_test</t>
+  </si>
+  <si>
+    <t>invalid_coin_denomination_test</t>
+  </si>
+  <si>
+    <t>insufficient_funds_test</t>
+  </si>
+  <si>
+    <t>coin_timeout_refund_test</t>
+  </si>
+  <si>
+    <t>confirm_timeout_refund_test</t>
   </si>
 </sst>
 </file>
@@ -927,22 +914,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
@@ -950,22 +937,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -973,22 +960,22 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -996,22 +983,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -1019,411 +1006,411 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="4" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>86</v>
+      <c r="B26" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -1431,22 +1418,22 @@
         <v>8</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>105</v>
+        <v>12</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -1454,123 +1441,101 @@
         <v>8</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>99</v>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
+    </row>
+    <row r="32" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
